--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iayz\PycharmProjects\architecture-sprint-9\Exc2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C2FC40-1AF9-405E-ADCC-DCB597B5EA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25E9323-C71B-4AAB-8B0A-AE910D5F9918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
